--- a/datasets/agenda_implementation/data/output/term_legislative_output.xlsx
+++ b/datasets/agenda_implementation/data/output/term_legislative_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['2025/0803(CNS)', '2025/0803(NLE)']</t>
+          <t>2025/0803(CNS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>['2025/0803(CNS)', '2025/0803(NLE)']</t>
+          <t>2025/0804(NLE)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2025-0803</t>
+          <t>2025-0804</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2025/0804(NLE)</t>
+          <t>2025/0805(NLE)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2025-0804</t>
+          <t>2025-0805</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2025/0805(NLE)</t>
+          <t>2025/0807(NLE)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2025-0805</t>
+          <t>2025-0807</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2025/0807(NLE)</t>
+          <t>2025/0808(NLE)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2025-0807</t>
+          <t>2025-0808</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2025/0808(NLE)</t>
+          <t>2025/0809(NLE)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2025-0808</t>
+          <t>2025-0809</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2025/0809(NLE)</t>
+          <t>2025/0810R(NLE)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2025-0809</t>
+          <t>2025-0810R</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2025/0810R(NLE)</t>
+          <t>2025/0901(NLE)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2025-0810R</t>
+          <t>2025-0901</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2025/0901(NLE)</t>
+          <t>2025/0902(NLE)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-0901</t>
+          <t>2025-0902</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2025/0902(NLE)</t>
+          <t>2025/0903(NLE)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2025-0902</t>
+          <t>2025-0903</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2025/0903(NLE)</t>
+          <t>2025/0904(NLE)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2025-0903</t>
+          <t>2025-0904</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2025/0904(NLE)</t>
+          <t>2025/0905(NLE)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2025-0904</t>
+          <t>2025-0905</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5852,12 +5852,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2025/0905(NLE)</t>
+          <t>2025/0906(NLE)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2025-0905</t>
+          <t>2025-0906</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2025/0906(NLE)</t>
+          <t>2026/0801(NLE)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2025-0906</t>
+          <t>2026-0801</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F166" t="b">
         <v>0</v>
@@ -5918,12 +5918,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026/0801(NLE)</t>
+          <t>2026/0802(NLE)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-0801</t>
+          <t>2026-0802</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5951,21 +5951,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026/0802(NLE)</t>
+          <t>2025/0256(APP)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-0802</t>
+          <t>2025-0256</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NLE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F168" t="b">
         <v>0</v>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2025/0256(APP)</t>
+          <t>2025/0571(APP)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2025-0256</t>
+          <t>2025-0571</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2025/0571(APP)</t>
+          <t>2025/3500(APP)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2025-0571</t>
+          <t>2025-3500</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -6037,39 +6037,6 @@
         <v>0</v>
       </c>
       <c r="G170" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>TO00170</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2025/3500(APP)</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2025-3500</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F171" t="b">
-        <v>0</v>
-      </c>
-      <c r="G171" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
